--- a/AAII_Financials/Yearly/OTEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OTEX_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/OTEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OTEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>OTEX</t>
   </si>
@@ -656,198 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44377</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44012</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43646</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43281</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42916</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42551</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42185</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41820</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41455</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41090</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5769600</v>
+      </c>
+      <c r="E8" s="3">
         <v>4485000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3493800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3386100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3109700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2868800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2815200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2291100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1824200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1851900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1624700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1363300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1207500</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1578500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1316600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1062200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1034500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1003800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>930700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>951000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>762400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>574000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>598400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>510700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>485900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>418000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4191000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3168400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2431600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2351600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2106000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1938100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1864200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1528700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1250200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1253500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1114000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>877400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>789500</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,50 +876,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>893900</v>
+      </c>
+      <c r="E12" s="3">
         <v>680600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>440400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>421400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>370400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>321800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>322900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>281700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>194100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>196500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>176800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>164000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>169000</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -947,93 +963,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-237400</v>
+      </c>
+      <c r="E14" s="3">
         <v>177300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>74300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>118300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>35700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>24200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-812500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>34800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>31300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>48100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>24500</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>564000</v>
+      </c>
+      <c r="E15" s="3">
         <v>434200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>305300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>301800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>309000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>287500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>271100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>215200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>168100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>159100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>116300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>93200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>74900</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,92 +1072,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>4509800</v>
+      </c>
+      <c r="E17" s="3">
         <v>3976800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2876500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2645200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2624100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2301700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2303500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1062000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1455700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1503200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1324200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1165700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1058100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1259800</v>
+      </c>
+      <c r="E18" s="3">
         <v>508100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>617400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>740900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>485700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>567000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>511700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1229000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>368600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>348700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>300500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>197700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>149400</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1149,218 +1181,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E20" s="3">
         <v>76800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>50200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>55500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>11100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>144100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>15700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-28000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-19500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-12000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2073200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1242300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1171500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1317000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1009100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1049000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1112700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1590500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>609500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>560800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>490600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>365100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>296800</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>535900</v>
+      </c>
+      <c r="E22" s="3">
         <v>363600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>151600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>145600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>149200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>137500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>269600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>119100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>76400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>54600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>27900</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>729300</v>
+      </c>
+      <c r="E23" s="3">
         <v>221300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>516000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>650800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>345200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>440600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>386100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1125700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>290800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>266000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>276500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>178200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>137300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E24" s="3">
         <v>70800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>118800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>339900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>110800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>154900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>124800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>99700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>31600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>58500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>29700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12200</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1400,93 +1448,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>465300</v>
+      </c>
+      <c r="E26" s="3">
         <v>150600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>397300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>310900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>234400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>285600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>261300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1025900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>284500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>234400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>218100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>148500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>125200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>465100</v>
+      </c>
+      <c r="E27" s="3">
         <v>150400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>397100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>310700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>234200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>285500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>261300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1025700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>284500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>234300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>218100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>148500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>125200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1526,9 +1583,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1544,14 +1604,14 @@
       <c r="G29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-19000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>17</v>
@@ -1568,9 +1628,12 @@
       <c r="O29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,9 +1673,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1652,93 +1718,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-76800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-50200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-55500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-11100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-144100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-15700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>28000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>19500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>12000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>465100</v>
+      </c>
+      <c r="E33" s="3">
         <v>150400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>397100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>310700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>234200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>285500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>242200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1025700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>284500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>234300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>218100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>148500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>125200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1778,98 +1853,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>465100</v>
+      </c>
+      <c r="E35" s="3">
         <v>150400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>397100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>310700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>234200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>285500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>242200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1025700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>284500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>234300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>218100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>148500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>125200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44377</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44012</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43646</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43281</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42916</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42551</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42185</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41820</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41455</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41090</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1886,8 +1970,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1904,58 +1989,62 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1280700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1231600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1693700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1607300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1692800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>941000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>682900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>443400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1283800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>700000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>427900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>470400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>559700</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E42" s="3">
         <v>1400</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>17</v>
@@ -1969,69 +2058,75 @@
       <c r="I42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
+      <c r="J42" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>11800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11200</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>17</v>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>757800</v>
+      </c>
+      <c r="E43" s="3">
         <v>828200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>471100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>496200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>557100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>523100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>543600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>478500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>317700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>305300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>317600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>371900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>350800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2071,219 +2166,237 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>237400</v>
+      </c>
+      <c r="E45" s="3">
         <v>213900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>120600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>98600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>136400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>97200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>101100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>81600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>59000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>83900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>70300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>54500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>48000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2277300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2275200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2285400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2202100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2386400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1561300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1327600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1003500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1672300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1069600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>815700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>717100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>789300</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>302300</v>
+      </c>
+      <c r="E47" s="3">
         <v>352200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>237000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>176400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>121000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>120400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>99500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>17900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13500</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>587500</v>
+      </c>
+      <c r="E48" s="3">
         <v>642600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>442800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>468100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>452400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>249500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>264200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>227400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>183700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>160400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>142300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16400</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9974600</v>
+      </c>
+      <c r="E49" s="3">
         <v>12743500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6319900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5878900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6284900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4916400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4876800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4889300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2971800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2841100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2665400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2671300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1665400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2323,9 +2436,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2365,51 +2481,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1063900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1075700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>893900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>883900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>990000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1086400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1197000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1320900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>299600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>283900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>292500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>247200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>222800</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2449,51 +2571,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14205700</v>
+      </c>
+      <c r="E54" s="3">
         <v>17089200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10179000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9609300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10234800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7934000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7765000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7480600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5154100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4353300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3899700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2654800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2444300</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2510,8 +2638,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2528,260 +2657,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>151200</v>
+      </c>
+      <c r="E57" s="3">
         <v>162700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>114000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>57500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>46300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7600</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E58" s="3">
         <v>326100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>10000</v>
       </c>
       <c r="F58" s="3">
         <v>10000</v>
       </c>
       <c r="G58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H58" s="3">
         <v>610000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>10000</v>
       </c>
       <c r="I58" s="3">
         <v>10000</v>
       </c>
       <c r="J58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K58" s="3">
         <v>182800</v>
-      </c>
-      <c r="K58" s="3">
-        <v>8000</v>
       </c>
       <c r="L58" s="3">
         <v>8000</v>
       </c>
       <c r="M58" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N58" s="3">
         <v>62600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>103500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>41400</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2610300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2730800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1344300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1294400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1252800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>958400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>942900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>900600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>627200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>601900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>562600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>595500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>493100</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2800500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3219600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1468300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1361900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1904200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1014700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>994600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1127000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>671000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>624400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>641200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>527900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>476500</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6359300</v>
+      </c>
+      <c r="E61" s="3">
         <v>8567600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4209600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3578900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3584300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2604900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2610500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2387100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2138000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1549400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1256800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>513800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>555000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>846300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1279900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>468900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>569100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>739600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>429700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>442600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>433100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>365900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>349700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>359600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>293800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>234500</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2821,9 +2969,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2863,9 +3014,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2905,51 +3059,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10007500</v>
+      </c>
+      <c r="E66" s="3">
         <v>13068400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6147900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5511400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6229400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4050500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4048800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3948200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3175500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2524000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2257800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1317600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1264900</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2966,8 +3126,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3007,9 +3168,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3049,9 +3213,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3091,9 +3258,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3133,51 +3303,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2119200</v>
+      </c>
+      <c r="E72" s="3">
         <v>2049000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2160100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2153300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2159400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2113900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1994200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1897600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>992500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>863000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>716300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>572900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>442100</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3217,9 +3393,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3259,9 +3438,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3301,51 +3483,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4198200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4020800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4031100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4097900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4005400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3883500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3716200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3532400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1978700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1829300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1641900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1337200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1179400</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3385,98 +3573,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44377</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44012</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43646</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43281</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42916</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42551</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42185</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41820</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41455</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41090</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>465100</v>
+      </c>
+      <c r="E81" s="3">
         <v>150400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>397100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>310700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>234200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>285500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>242200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1025700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>284500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>234300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>218100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>148500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>125200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3493,50 +3690,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>807900</v>
+      </c>
+      <c r="E83" s="3">
         <v>657400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>504000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>520600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>514700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>470900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>456900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>345700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>242400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>240100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>186200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>186900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>159500</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3576,9 +3777,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3618,9 +3822,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3660,9 +3867,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3702,9 +3912,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3744,51 +3957,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>967700</v>
+      </c>
+      <c r="E89" s="3">
         <v>779200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>981800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>876100</v>
       </c>
-      <c r="G89" s="3">
-        <v>954500</v>
-      </c>
       <c r="H89" s="3">
+        <v>948700</v>
+      </c>
+      <c r="I89" s="3">
         <v>876300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>708100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>439300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>525700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>523000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>417100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>318500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>266500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3805,50 +4024,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-159300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-123800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-93100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-72700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-63800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-105300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-79600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-70000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-77000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-42300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25800</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3888,9 +4111,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3930,51 +4156,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2055300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5651400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-971000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-68800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1469400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-464500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-444400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2191000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-361200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-398400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1153400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-374400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-281500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3991,50 +4223,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-267400</v>
+      </c>
+      <c r="E96" s="3">
         <v>-259500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-237700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-210700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-188700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-168900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-145600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-120600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-99300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-87600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-17700</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4074,9 +4310,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4116,9 +4355,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4158,133 +4400,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2961900</v>
+      </c>
+      <c r="E100" s="3">
         <v>4403100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>138500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-924500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1268800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-148400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-23700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>909500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>430200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>170600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>687900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-31100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>302600</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E101" s="3">
         <v>7200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-63200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>29700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-23100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11900</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-462000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>86100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-87500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>753700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>259600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>237800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-840400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>583800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>272100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-42600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-89300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>275600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/OTEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OTEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>OTEX</t>
   </si>
@@ -774,25 +774,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1578500</v>
+        <v>1334600</v>
       </c>
       <c r="E9" s="3">
-        <v>1316600</v>
+        <v>1093400</v>
       </c>
       <c r="F9" s="3">
-        <v>1062200</v>
+        <v>863600</v>
       </c>
       <c r="G9" s="3">
-        <v>1034500</v>
+        <v>815700</v>
       </c>
       <c r="H9" s="3">
-        <v>1003800</v>
+        <v>798100</v>
       </c>
       <c r="I9" s="3">
-        <v>930700</v>
+        <v>747300</v>
       </c>
       <c r="J9" s="3">
-        <v>951000</v>
+        <v>765100</v>
       </c>
       <c r="K9" s="3">
         <v>762400</v>
@@ -819,25 +819,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4191000</v>
+        <v>4435000</v>
       </c>
       <c r="E10" s="3">
-        <v>3168400</v>
+        <v>3391600</v>
       </c>
       <c r="F10" s="3">
-        <v>2431600</v>
+        <v>2630300</v>
       </c>
       <c r="G10" s="3">
-        <v>2351600</v>
+        <v>2570400</v>
       </c>
       <c r="H10" s="3">
-        <v>2106000</v>
+        <v>2311700</v>
       </c>
       <c r="I10" s="3">
-        <v>1938100</v>
+        <v>2121400</v>
       </c>
       <c r="J10" s="3">
-        <v>1864200</v>
+        <v>2050100</v>
       </c>
       <c r="K10" s="3">
         <v>1528700</v>
@@ -991,7 +991,7 @@
         <v>35700</v>
       </c>
       <c r="J14" s="3">
-        <v>24200</v>
+        <v>23400</v>
       </c>
       <c r="K14" s="3">
         <v>-812500</v>
@@ -1018,25 +1018,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>564000</v>
+        <v>807900</v>
       </c>
       <c r="E15" s="3">
-        <v>434200</v>
+        <v>657400</v>
       </c>
       <c r="F15" s="3">
-        <v>305300</v>
+        <v>504000</v>
       </c>
       <c r="G15" s="3">
-        <v>301800</v>
+        <v>520600</v>
       </c>
       <c r="H15" s="3">
-        <v>309000</v>
+        <v>514700</v>
       </c>
       <c r="I15" s="3">
-        <v>287500</v>
+        <v>470900</v>
       </c>
       <c r="J15" s="3">
-        <v>271100</v>
+        <v>456900</v>
       </c>
       <c r="K15" s="3">
         <v>215200</v>
@@ -1079,25 +1079,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>4509800</v>
+        <v>4760200</v>
       </c>
       <c r="E17" s="3">
-        <v>3976800</v>
+        <v>3806900</v>
       </c>
       <c r="F17" s="3">
-        <v>2876500</v>
+        <v>2805500</v>
       </c>
       <c r="G17" s="3">
-        <v>2645200</v>
+        <v>2646600</v>
       </c>
       <c r="H17" s="3">
-        <v>2624100</v>
+        <v>2507800</v>
       </c>
       <c r="I17" s="3">
-        <v>2301700</v>
+        <v>2267700</v>
       </c>
       <c r="J17" s="3">
-        <v>2303500</v>
+        <v>2281000</v>
       </c>
       <c r="K17" s="3">
         <v>1062000</v>
@@ -1124,25 +1124,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1259800</v>
+        <v>1009400</v>
       </c>
       <c r="E18" s="3">
-        <v>508100</v>
+        <v>678100</v>
       </c>
       <c r="F18" s="3">
-        <v>617400</v>
+        <v>688400</v>
       </c>
       <c r="G18" s="3">
-        <v>740900</v>
+        <v>739500</v>
       </c>
       <c r="H18" s="3">
-        <v>485700</v>
+        <v>601900</v>
       </c>
       <c r="I18" s="3">
-        <v>567000</v>
+        <v>601000</v>
       </c>
       <c r="J18" s="3">
-        <v>511700</v>
+        <v>534200</v>
       </c>
       <c r="K18" s="3">
         <v>1229000</v>
@@ -1188,25 +1188,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>5400</v>
+        <v>30700</v>
       </c>
       <c r="E20" s="3">
-        <v>76800</v>
+        <v>-30700</v>
       </c>
       <c r="F20" s="3">
-        <v>50200</v>
+        <v>-48900</v>
       </c>
       <c r="G20" s="3">
-        <v>55500</v>
+        <v>-54800</v>
       </c>
       <c r="H20" s="3">
-        <v>8700</v>
+        <v>1000</v>
       </c>
       <c r="I20" s="3">
-        <v>11100</v>
+        <v>-4700</v>
       </c>
       <c r="J20" s="3">
-        <v>144100</v>
+        <v>-6000</v>
       </c>
       <c r="K20" s="3">
         <v>15700</v>
@@ -1233,25 +1233,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>2073200</v>
+        <v>1786600</v>
       </c>
       <c r="E21" s="3">
-        <v>1242300</v>
+        <v>1366100</v>
       </c>
       <c r="F21" s="3">
-        <v>1171500</v>
+        <v>1241200</v>
       </c>
       <c r="G21" s="3">
-        <v>1317000</v>
+        <v>1314900</v>
       </c>
       <c r="H21" s="3">
-        <v>1009100</v>
+        <v>1115700</v>
       </c>
       <c r="I21" s="3">
-        <v>1049000</v>
+        <v>1076700</v>
       </c>
       <c r="J21" s="3">
-        <v>1112700</v>
+        <v>997100</v>
       </c>
       <c r="K21" s="3">
         <v>1590500</v>
@@ -1296,7 +1296,7 @@
         <v>137500</v>
       </c>
       <c r="J22" s="3">
-        <v>269600</v>
+        <v>132400</v>
       </c>
       <c r="K22" s="3">
         <v>119100</v>
@@ -1386,7 +1386,7 @@
         <v>154900</v>
       </c>
       <c r="J24" s="3">
-        <v>124800</v>
+        <v>143800</v>
       </c>
       <c r="K24" s="3">
         <v>99700</v>
@@ -1476,7 +1476,7 @@
         <v>285600</v>
       </c>
       <c r="J26" s="3">
-        <v>261300</v>
+        <v>242300</v>
       </c>
       <c r="K26" s="3">
         <v>1025900</v>
@@ -1521,7 +1521,7 @@
         <v>285500</v>
       </c>
       <c r="J27" s="3">
-        <v>261300</v>
+        <v>242200</v>
       </c>
       <c r="K27" s="3">
         <v>1025700</v>
@@ -1592,26 +1592,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>17</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-19000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>17</v>
@@ -1728,25 +1728,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5400</v>
+        <v>-30700</v>
       </c>
       <c r="E32" s="3">
-        <v>-76800</v>
+        <v>30700</v>
       </c>
       <c r="F32" s="3">
-        <v>-50200</v>
+        <v>48900</v>
       </c>
       <c r="G32" s="3">
-        <v>-55500</v>
+        <v>54800</v>
       </c>
       <c r="H32" s="3">
-        <v>-8700</v>
+        <v>-1000</v>
       </c>
       <c r="I32" s="3">
-        <v>-11100</v>
+        <v>4700</v>
       </c>
       <c r="J32" s="3">
-        <v>-144100</v>
+        <v>6000</v>
       </c>
       <c r="K32" s="3">
         <v>-15700</v>
@@ -2008,7 +2008,7 @@
         <v>1607300</v>
       </c>
       <c r="H41" s="3">
-        <v>1692800</v>
+        <v>1692900</v>
       </c>
       <c r="I41" s="3">
         <v>941000</v>
@@ -2041,25 +2041,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1500</v>
+        <v>4100</v>
       </c>
       <c r="E42" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>17</v>
+        <v>2600</v>
+      </c>
+      <c r="F42" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H42" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2086,10 +2086,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>757800</v>
+        <v>753800</v>
       </c>
       <c r="E43" s="3">
-        <v>828200</v>
+        <v>821900</v>
       </c>
       <c r="F43" s="3">
         <v>471100</v>
@@ -2130,26 +2130,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2176,25 +2176,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>237400</v>
+        <v>46700</v>
       </c>
       <c r="E45" s="3">
-        <v>213900</v>
+        <v>43200</v>
       </c>
       <c r="F45" s="3">
-        <v>120600</v>
+        <v>27100</v>
       </c>
       <c r="G45" s="3">
-        <v>98600</v>
+        <v>23700</v>
       </c>
       <c r="H45" s="3">
-        <v>136400</v>
+        <v>18100</v>
       </c>
       <c r="I45" s="3">
-        <v>97200</v>
+        <v>13400</v>
       </c>
       <c r="J45" s="3">
-        <v>101100</v>
+        <v>22100</v>
       </c>
       <c r="K45" s="3">
         <v>81600</v>
@@ -2266,25 +2266,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>302300</v>
+        <v>164700</v>
       </c>
       <c r="E47" s="3">
-        <v>352200</v>
+        <v>187800</v>
       </c>
       <c r="F47" s="3">
-        <v>237000</v>
+        <v>173200</v>
       </c>
       <c r="G47" s="3">
-        <v>176400</v>
+        <v>121800</v>
       </c>
       <c r="H47" s="3">
-        <v>121000</v>
+        <v>76000</v>
       </c>
       <c r="I47" s="3">
-        <v>120400</v>
+        <v>67000</v>
       </c>
       <c r="J47" s="3">
-        <v>99500</v>
+        <v>49600</v>
       </c>
       <c r="K47" s="3">
         <v>39500</v>
@@ -2311,25 +2311,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>587500</v>
+        <v>449600</v>
       </c>
       <c r="E48" s="3">
-        <v>642600</v>
+        <v>504800</v>
       </c>
       <c r="F48" s="3">
-        <v>442800</v>
+        <v>370600</v>
       </c>
       <c r="G48" s="3">
-        <v>468100</v>
+        <v>401900</v>
       </c>
       <c r="H48" s="3">
-        <v>452400</v>
+        <v>387000</v>
       </c>
       <c r="I48" s="3">
-        <v>249500</v>
+        <v>178200</v>
       </c>
       <c r="J48" s="3">
-        <v>264200</v>
+        <v>186500</v>
       </c>
       <c r="K48" s="3">
         <v>227400</v>
@@ -2356,25 +2356,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9974600</v>
+        <v>10112500</v>
       </c>
       <c r="E49" s="3">
-        <v>12743500</v>
+        <v>12881300</v>
       </c>
       <c r="F49" s="3">
-        <v>6319900</v>
+        <v>6392100</v>
       </c>
       <c r="G49" s="3">
-        <v>5878900</v>
+        <v>5945200</v>
       </c>
       <c r="H49" s="3">
-        <v>6284900</v>
+        <v>6350300</v>
       </c>
       <c r="I49" s="3">
-        <v>4916400</v>
+        <v>4987700</v>
       </c>
       <c r="J49" s="3">
-        <v>4876800</v>
+        <v>4954500</v>
       </c>
       <c r="K49" s="3">
         <v>4889300</v>
@@ -2491,25 +2491,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1063900</v>
+        <v>165300</v>
       </c>
       <c r="E52" s="3">
-        <v>1075700</v>
+        <v>191200</v>
       </c>
       <c r="F52" s="3">
-        <v>893900</v>
+        <v>72300</v>
       </c>
       <c r="G52" s="3">
-        <v>883900</v>
+        <v>72200</v>
       </c>
       <c r="H52" s="3">
-        <v>990000</v>
+        <v>65100</v>
       </c>
       <c r="I52" s="3">
-        <v>1086400</v>
+        <v>84400</v>
       </c>
       <c r="J52" s="3">
-        <v>1197000</v>
+        <v>59300</v>
       </c>
       <c r="K52" s="3">
         <v>1320900</v>
@@ -2709,19 +2709,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>39000</v>
+        <v>115500</v>
       </c>
       <c r="E58" s="3">
-        <v>326100</v>
+        <v>417600</v>
       </c>
       <c r="F58" s="3">
-        <v>10000</v>
+        <v>66400</v>
       </c>
       <c r="G58" s="3">
-        <v>10000</v>
+        <v>68300</v>
       </c>
       <c r="H58" s="3">
-        <v>610000</v>
+        <v>674100</v>
       </c>
       <c r="I58" s="3">
         <v>10000</v>
@@ -2754,25 +2754,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2610300</v>
+        <v>1947000</v>
       </c>
       <c r="E59" s="3">
-        <v>2730800</v>
+        <v>2008300</v>
       </c>
       <c r="F59" s="3">
-        <v>1344300</v>
+        <v>961600</v>
       </c>
       <c r="G59" s="3">
-        <v>1294400</v>
+        <v>876300</v>
       </c>
       <c r="H59" s="3">
-        <v>1252800</v>
+        <v>873400</v>
       </c>
       <c r="I59" s="3">
-        <v>958400</v>
+        <v>684600</v>
       </c>
       <c r="J59" s="3">
-        <v>942900</v>
+        <v>691200</v>
       </c>
       <c r="K59" s="3">
         <v>900600</v>
@@ -2844,19 +2844,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6359300</v>
+        <v>6577400</v>
       </c>
       <c r="E61" s="3">
-        <v>8567600</v>
+        <v>8839200</v>
       </c>
       <c r="F61" s="3">
-        <v>4209600</v>
+        <v>4408300</v>
       </c>
       <c r="G61" s="3">
-        <v>3578900</v>
+        <v>3803300</v>
       </c>
       <c r="H61" s="3">
-        <v>3584300</v>
+        <v>3801500</v>
       </c>
       <c r="I61" s="3">
         <v>2604900</v>
@@ -2889,25 +2889,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>846300</v>
+        <v>189800</v>
       </c>
       <c r="E62" s="3">
-        <v>1279900</v>
+        <v>240300</v>
       </c>
       <c r="F62" s="3">
-        <v>468900</v>
+        <v>52200</v>
       </c>
       <c r="G62" s="3">
-        <v>569100</v>
+        <v>62900</v>
       </c>
       <c r="H62" s="3">
-        <v>739600</v>
+        <v>206200</v>
       </c>
       <c r="I62" s="3">
-        <v>429700</v>
+        <v>251600</v>
       </c>
       <c r="J62" s="3">
-        <v>442600</v>
+        <v>227800</v>
       </c>
       <c r="K62" s="3">
         <v>433100</v>
@@ -3069,25 +3069,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10007500</v>
+        <v>10006000</v>
       </c>
       <c r="E66" s="3">
-        <v>13068400</v>
+        <v>13067100</v>
       </c>
       <c r="F66" s="3">
-        <v>6147900</v>
+        <v>6146700</v>
       </c>
       <c r="G66" s="3">
-        <v>5511400</v>
+        <v>5509900</v>
       </c>
       <c r="H66" s="3">
-        <v>6229400</v>
+        <v>6228100</v>
       </c>
       <c r="I66" s="3">
-        <v>4050500</v>
+        <v>4049300</v>
       </c>
       <c r="J66" s="3">
-        <v>4048800</v>
+        <v>4047800</v>
       </c>
       <c r="K66" s="3">
         <v>3948200</v>
@@ -3697,25 +3697,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>807900</v>
+        <v>131600</v>
       </c>
       <c r="E83" s="3">
-        <v>657400</v>
+        <v>107800</v>
       </c>
       <c r="F83" s="3">
-        <v>504000</v>
+        <v>88200</v>
       </c>
       <c r="G83" s="3">
-        <v>520600</v>
+        <v>85300</v>
       </c>
       <c r="H83" s="3">
-        <v>514700</v>
+        <v>89500</v>
       </c>
       <c r="I83" s="3">
-        <v>470900</v>
+        <v>97700</v>
       </c>
       <c r="J83" s="3">
-        <v>456900</v>
+        <v>86900</v>
       </c>
       <c r="K83" s="3">
         <v>345700</v>
@@ -3979,7 +3979,7 @@
         <v>876100</v>
       </c>
       <c r="H89" s="3">
-        <v>948700</v>
+        <v>954500</v>
       </c>
       <c r="I89" s="3">
         <v>876300</v>
@@ -4230,25 +4230,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-267400</v>
+        <v>267400</v>
       </c>
       <c r="E96" s="3">
-        <v>-259500</v>
+        <v>259500</v>
       </c>
       <c r="F96" s="3">
-        <v>-237700</v>
+        <v>237700</v>
       </c>
       <c r="G96" s="3">
-        <v>-210700</v>
+        <v>210700</v>
       </c>
       <c r="H96" s="3">
-        <v>-188700</v>
+        <v>188700</v>
       </c>
       <c r="I96" s="3">
-        <v>-168900</v>
+        <v>168900</v>
       </c>
       <c r="J96" s="3">
-        <v>-145600</v>
+        <v>145600</v>
       </c>
       <c r="K96" s="3">
         <v>-120600</v>

--- a/AAII_Financials/Yearly/OTEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OTEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>OTEX</t>
   </si>
@@ -656,210 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44377</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44012</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43646</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43281</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42916</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42551</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42185</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41820</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41455</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41090</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5168400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5769600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4485000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3493800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3386100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3109700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2868800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2815200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2291100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1824200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1851900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1624700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1363300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1207500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1245300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1334600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1093400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>863600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>815700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>798100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>747300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>765100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>762400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>574000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>598400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>510700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>485900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>418000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3923100</v>
+      </c>
+      <c r="E10" s="3">
         <v>4435000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3391600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2630300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2570400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2311700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2121400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2050100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1528700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1250200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1253500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1114000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>877400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>789500</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -877,53 +889,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>893900</v>
+        <v>755900</v>
       </c>
       <c r="E12" s="3">
-        <v>680600</v>
+        <v>864500</v>
       </c>
       <c r="F12" s="3">
+        <v>659200</v>
+      </c>
+      <c r="G12" s="3">
         <v>440400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>421400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>370400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>321800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>322900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>281700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>194100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>196500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>176800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>164000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>169000</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,99 +982,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>150100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-237400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>177300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>74300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>118300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>35700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>23400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-812500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>34800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>31300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>48100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>24500</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>641200</v>
+      </c>
+      <c r="E15" s="3">
         <v>807900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>657400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>504000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>520600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>514700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>470900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>456900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>215200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>168100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>159100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>116300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>93200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>74900</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1073,98 +1098,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>4144100</v>
+      </c>
+      <c r="E17" s="3">
         <v>4760200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3806900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2805500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2646600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2507800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2267700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2281000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1062000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1455700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1503200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1324200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1165700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1058100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1024300</v>
+      </c>
+      <c r="E18" s="3">
         <v>1009400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>678100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>688400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>739500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>601900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>601000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>534200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1229000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>368600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>348700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>300500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>197700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>149400</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1182,233 +1214,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E20" s="3">
         <v>30700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-30700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-48900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-54800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>15700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-28000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-19500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1575200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1786600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1366100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1241200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1314900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1115700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1076700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>997100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1590500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>609500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>560800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>490600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>365100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>296800</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>351400</v>
+      </c>
+      <c r="E22" s="3">
         <v>535900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>363600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>151600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>145600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>149200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>137500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>132400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>119100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>76400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>54600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>27900</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>482100</v>
+      </c>
+      <c r="E23" s="3">
         <v>729300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>221300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>516000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>650800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>345200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>440600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>386100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1125700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>290800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>266000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>276500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>178200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>137300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E24" s="3">
         <v>264000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>70800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>118800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>339900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>110800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>154900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>143800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>99700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>31600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>58500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>29700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12200</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1451,99 +1499,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>436100</v>
+      </c>
+      <c r="E26" s="3">
         <v>465300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>150600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>397300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>310900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>234400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>285600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>242300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1025900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>284500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>234400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>218100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>148500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>125200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>435900</v>
+      </c>
+      <c r="E27" s="3">
         <v>465100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>150400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>397100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>310700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>234200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>285500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>242200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1025700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>284500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>234300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>218100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>148500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>125200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1586,9 +1643,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1673,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>17</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>17</v>
@@ -1631,9 +1691,12 @@
       <c r="P29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1676,9 +1739,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1721,99 +1787,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-90300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-30700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>30700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>48900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>54800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-15700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>28000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>19500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>12000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>435900</v>
+      </c>
+      <c r="E33" s="3">
         <v>465100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>150400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>397100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>310700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>234200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>285500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>242200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1025700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>284500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>234300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>218100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>148500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>125200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1856,104 +1931,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>435900</v>
+      </c>
+      <c r="E35" s="3">
         <v>465100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>150400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>397100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>310700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>234200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>285500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>242200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1025700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>284500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>234300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>218100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>148500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>125200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44377</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44012</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43646</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43281</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42916</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42551</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42185</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41820</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41455</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41090</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1971,8 +2055,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1990,74 +2075,78 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1156500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1280700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1231600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1693700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1607300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1692900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>941000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>682900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>443400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1283800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>700000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>427900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>470400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>559700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E42" s="3">
         <v>4100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7500</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2065,68 +2154,74 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>11800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11200</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>17</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>846400</v>
+      </c>
+      <c r="E43" s="3">
         <v>753800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>821900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>471100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>496200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>557100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>523100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>543600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>478500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>317700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>305300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>317600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>371900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>350800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2151,8 +2246,8 @@
       <c r="J44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2169,234 +2264,252 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E45" s="3">
         <v>46700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>43200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>81600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>59000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>83900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>70300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>54500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>48000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2201500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2277300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2275200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2285400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2202100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2386400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1561300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1327600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1003500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1672300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1069600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>815700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>717100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>789300</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>161800</v>
+      </c>
+      <c r="E47" s="3">
         <v>164700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>187800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>173200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>121800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>76000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>67000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>49600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>26800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>17900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13500</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E48" s="3">
         <v>449600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>504800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>370600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>401900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>387000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>178200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>186500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>227400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>183700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>160400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>142300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9627300</v>
+      </c>
+      <c r="E49" s="3">
         <v>10112500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12881300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6392100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5945200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6350300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4987700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4954500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4889300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2971800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2841100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2665400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2671300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1665400</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2439,9 +2552,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2484,54 +2600,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E52" s="3">
         <v>165300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>191200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>72300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>72200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>65100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>84400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>59300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1320900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>299600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>283900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>292500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>247200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>222800</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2574,54 +2696,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13774100</v>
+      </c>
+      <c r="E54" s="3">
         <v>14205700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17089200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10179000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9609300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10234800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7934000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7765000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7480600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5154100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4353300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3899700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2654800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2444300</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2639,8 +2767,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2658,278 +2787,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>136200</v>
+      </c>
+      <c r="E57" s="3">
         <v>151200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>162700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>114000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>57500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>46300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7600</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>113600</v>
+      </c>
+      <c r="E58" s="3">
         <v>115500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>417600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>66400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>68300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>674100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>10000</v>
       </c>
       <c r="J58" s="3">
         <v>10000</v>
       </c>
       <c r="K58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L58" s="3">
         <v>182800</v>
-      </c>
-      <c r="L58" s="3">
-        <v>8000</v>
       </c>
       <c r="M58" s="3">
         <v>8000</v>
       </c>
       <c r="N58" s="3">
+        <v>8000</v>
+      </c>
+      <c r="O58" s="3">
         <v>62600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>103500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>41400</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1945100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1947000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2008300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>961600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>876300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>873400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>684600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>691200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>900600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>627200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>601900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>562600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>595500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>493100</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2747100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2800500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3219600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1468300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1361900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1904200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1014700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>994600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1127000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>671000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>624400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>641200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>527900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>476500</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6532500</v>
+      </c>
+      <c r="E61" s="3">
         <v>6577400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8839200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4408300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3803300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3801500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2604900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2610500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2387100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2138000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1549400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1256800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>513800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>555000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>121500</v>
+      </c>
+      <c r="E62" s="3">
         <v>189800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>240300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>52200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>62900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>206200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>251600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>227800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>433100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>365900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>349700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>359600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>293800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>234500</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2972,9 +3120,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3017,9 +3168,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3062,54 +3216,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9843500</v>
+      </c>
+      <c r="E66" s="3">
         <v>10006000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13067100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6146700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5509900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6228100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4049300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4047800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3948200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3175500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2524000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2257800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1317600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1264900</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3127,8 +3287,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3171,9 +3332,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3216,9 +3380,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3261,9 +3428,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3306,54 +3476,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1940100</v>
+      </c>
+      <c r="E72" s="3">
         <v>2119200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2049000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2160100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2153300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2159400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2113900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1994200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1897600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>992500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>863000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>716300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>572900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>442100</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3396,9 +3572,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3441,9 +3620,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3486,54 +3668,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3928900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4198200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4020800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4031100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4097900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4005400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3883500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3716200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3532400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1978700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1829300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1641900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1337200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1179400</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3576,104 +3764,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44377</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44012</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43646</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43281</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42916</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42551</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42185</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41820</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41455</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41090</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>435900</v>
+      </c>
+      <c r="E81" s="3">
         <v>465100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>150400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>397100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>310700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>234200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>285500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>242200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1025700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>284500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>234300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>218100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>148500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>125200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3691,53 +3888,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>130600</v>
+      </c>
+      <c r="E83" s="3">
         <v>131600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>107800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>88200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>85300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>89500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>97700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>86900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>345700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>242400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>240100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>186200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>186900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>159500</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3780,9 +3981,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3825,9 +4029,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3870,9 +4077,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3915,9 +4125,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3960,54 +4173,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>830600</v>
+      </c>
+      <c r="E89" s="3">
         <v>967700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>779200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>981800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>876100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>954500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>876300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>708100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>439300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>525700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>523000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>417100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>318500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>266500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4025,53 +4244,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-143200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-159300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-123800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-93100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-63700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-72700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-63800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-105300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-79600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-70000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-77000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4114,9 +4337,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4159,54 +4385,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-153500</v>
+      </c>
+      <c r="E94" s="3">
         <v>2055300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5651400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-971000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-68800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1469400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-464500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-444400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2191000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-361200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-398400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1153400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-374400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-281500</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4224,53 +4456,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>271500</v>
+      </c>
+      <c r="E96" s="3">
         <v>267400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>259500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>237700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>210700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>188700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>168900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>145600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-120600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-99300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-87600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-17700</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4313,9 +4549,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4358,9 +4597,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4403,142 +4645,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-834700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2961900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4403100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>138500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-924500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1268800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-148400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-23700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>909500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>430200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>170600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>687900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-31100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>302600</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-63200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>29700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-23100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-124700</v>
+      </c>
+      <c r="E102" s="3">
         <v>48800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-462000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>86100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-87500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>753700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>259600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>237800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-840400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>583800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>272100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-42600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-89300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>275600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
